--- a/results/allTranscripts.xlsx
+++ b/results/allTranscripts.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1850" uniqueCount="1767">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1850" uniqueCount="1766">
   <si>
     <t xml:space="preserve">Sentence number</t>
   </si>
@@ -313,13 +313,13 @@
     <t xml:space="preserve">especially the ones that came out and said their piece</t>
   </si>
   <si>
-    <t xml:space="preserve">Its sped you whats a canal set through piece.</t>
+    <t xml:space="preserve">Its sped you whats a canal set through piece</t>
   </si>
   <si>
     <t xml:space="preserve">Ones they came out said their piece</t>
   </si>
   <si>
-    <t xml:space="preserve">Its visioner came out and said their peace</t>
+    <t xml:space="preserve">Its visioner came out and said their piece</t>
   </si>
   <si>
     <t xml:space="preserve">my ankle feels softer now</t>
@@ -640,7 +640,7 @@
     <t xml:space="preserve">thats kind of like what wed like to do</t>
   </si>
   <si>
-    <t xml:space="preserve">Thats kind of like what we would like to do</t>
+    <t xml:space="preserve">Thats kind of like what wed like to do</t>
   </si>
   <si>
     <t xml:space="preserve">Thats kind of wed like to do</t>
@@ -1381,7 +1381,7 @@
     <t xml:space="preserve">Is it ted oh</t>
   </si>
   <si>
-    <t xml:space="preserve">Is it 10 now</t>
+    <t xml:space="preserve">Is it ten now</t>
   </si>
   <si>
     <t xml:space="preserve">Is it tedo</t>
@@ -1573,7 +1573,7 @@
     <t xml:space="preserve">Weak team </t>
   </si>
   <si>
-    <t xml:space="preserve">We team 77s</t>
+    <t xml:space="preserve">We teams</t>
   </si>
   <si>
     <t xml:space="preserve">the hard back copy of it</t>
@@ -2362,7 +2362,7 @@
     <t xml:space="preserve">just about anybody you could name</t>
   </si>
   <si>
-    <t xml:space="preserve">That's about any money youve gained</t>
+    <t xml:space="preserve">Thats about any money youve gained</t>
   </si>
   <si>
     <t xml:space="preserve">Ask about anybody you may</t>
@@ -2395,7 +2395,7 @@
     <t xml:space="preserve">If were many years happened</t>
   </si>
   <si>
-    <t xml:space="preserve">that might be too crude to be called woodworking</t>
+    <t xml:space="preserve">that might be too crude to be called wood working</t>
   </si>
   <si>
     <t xml:space="preserve">That might to be cold when working</t>
@@ -2824,7 +2824,7 @@
     <t xml:space="preserve">its nice to get out in the open air</t>
   </si>
   <si>
-    <t xml:space="preserve">It's nice to get out in the </t>
+    <t xml:space="preserve">Its nice to get out in the </t>
   </si>
   <si>
     <t xml:space="preserve">its nice to get out of the </t>
@@ -3061,7 +3061,7 @@
     <t xml:space="preserve">You think that its a pretty</t>
   </si>
   <si>
-    <t xml:space="preserve">You think that's ready cap sent in </t>
+    <t xml:space="preserve">You think thats ready cap sent in </t>
   </si>
   <si>
     <t xml:space="preserve">it can swim away fast enough and go hide</t>
@@ -3745,7 +3745,7 @@
     <t xml:space="preserve">Used to being six spots </t>
   </si>
   <si>
-    <t xml:space="preserve">Used to be 6 spots</t>
+    <t xml:space="preserve">Used to be six spots</t>
   </si>
   <si>
     <t xml:space="preserve">Used to be six bucks</t>
@@ -3778,7 +3778,7 @@
     <t xml:space="preserve">they can get away with one guy like that</t>
   </si>
   <si>
-    <t xml:space="preserve">Thanking you to May with one I don’t like that </t>
+    <t xml:space="preserve">Thanking you to May with one I dont like that </t>
   </si>
   <si>
     <t xml:space="preserve">Baking with one I like that</t>
@@ -4221,7 +4221,7 @@
     <t xml:space="preserve">Now thats exciting again</t>
   </si>
   <si>
-    <t xml:space="preserve">Now that's exciting in</t>
+    <t xml:space="preserve">Now thats exciting in</t>
   </si>
   <si>
     <t xml:space="preserve">if you let one little law get through</t>
@@ -4287,7 +4287,7 @@
     <t xml:space="preserve">I quill  is all I think about </t>
   </si>
   <si>
-    <t xml:space="preserve">I could lie by window that's all I think about</t>
+    <t xml:space="preserve">I could lie by window thats all I think about</t>
   </si>
   <si>
     <t xml:space="preserve">A quill I when I thats all I think about</t>
@@ -4650,7 +4650,7 @@
     <t xml:space="preserve">The clay were stiff in the moll </t>
   </si>
   <si>
-    <t xml:space="preserve">The worst is 7 mall</t>
+    <t xml:space="preserve">The worst is seven mall</t>
   </si>
   <si>
     <t xml:space="preserve">A claim were still seven more</t>
@@ -4830,7 +4830,7 @@
     <t xml:space="preserve">His camera was full by</t>
   </si>
   <si>
-    <t xml:space="preserve">It's tie camera was fooled by supreme</t>
+    <t xml:space="preserve">Its tie camera was fooled by supreme</t>
   </si>
   <si>
     <t xml:space="preserve">you can program the one at cosmopolitan lady</t>
@@ -4911,7 +4911,7 @@
     <t xml:space="preserve">All need  out </t>
   </si>
   <si>
-    <t xml:space="preserve">Only 3 down</t>
+    <t xml:space="preserve">Only three down</t>
   </si>
   <si>
     <t xml:space="preserve">Dont make fred out</t>
@@ -5020,9 +5020,6 @@
   </si>
   <si>
     <t xml:space="preserve">I still dont know</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I still don’t know</t>
   </si>
   <si>
     <t xml:space="preserve">they have a new one now</t>
@@ -5368,7 +5365,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -5397,12 +5394,6 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -5467,7 +5458,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5486,10 +5477,6 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -5576,7 +5563,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="49.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="40.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="38.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="38.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="29.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="40.24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="25.11"/>
@@ -6790,7 +6777,7 @@
       <c r="C37" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="D37" s="1" t="s">
         <v>277</v>
       </c>
       <c r="E37" s="1" t="s">
@@ -12956,7 +12943,7 @@
         <v>1653</v>
       </c>
       <c r="E372" s="1" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="373" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12964,16 +12951,16 @@
         <v>372</v>
       </c>
       <c r="B373" s="1" t="s">
+        <v>1654</v>
+      </c>
+      <c r="C373" s="1" t="s">
         <v>1655</v>
       </c>
-      <c r="C373" s="1" t="s">
+      <c r="D373" s="1" t="s">
         <v>1656</v>
       </c>
-      <c r="D373" s="1" t="s">
+      <c r="E373" s="1" t="s">
         <v>1657</v>
-      </c>
-      <c r="E373" s="1" t="s">
-        <v>1658</v>
       </c>
     </row>
     <row r="374" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12981,16 +12968,16 @@
         <v>373</v>
       </c>
       <c r="B374" s="1" t="s">
+        <v>1658</v>
+      </c>
+      <c r="C374" s="1" t="s">
         <v>1659</v>
       </c>
-      <c r="C374" s="1" t="s">
+      <c r="D374" s="1" t="s">
         <v>1660</v>
       </c>
-      <c r="D374" s="1" t="s">
+      <c r="E374" s="1" t="s">
         <v>1661</v>
-      </c>
-      <c r="E374" s="1" t="s">
-        <v>1662</v>
       </c>
     </row>
     <row r="375" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12998,16 +12985,16 @@
         <v>374</v>
       </c>
       <c r="B375" s="1" t="s">
+        <v>1662</v>
+      </c>
+      <c r="C375" s="1" t="s">
         <v>1663</v>
       </c>
-      <c r="C375" s="1" t="s">
+      <c r="D375" s="1" t="s">
         <v>1664</v>
       </c>
-      <c r="D375" s="1" t="s">
+      <c r="E375" s="1" t="s">
         <v>1665</v>
-      </c>
-      <c r="E375" s="1" t="s">
-        <v>1666</v>
       </c>
     </row>
     <row r="376" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13015,16 +13002,16 @@
         <v>375</v>
       </c>
       <c r="B376" s="1" t="s">
+        <v>1666</v>
+      </c>
+      <c r="C376" s="1" t="s">
         <v>1667</v>
       </c>
-      <c r="C376" s="1" t="s">
+      <c r="D376" s="1" t="s">
         <v>1668</v>
       </c>
-      <c r="D376" s="1" t="s">
+      <c r="E376" s="1" t="s">
         <v>1669</v>
-      </c>
-      <c r="E376" s="1" t="s">
-        <v>1670</v>
       </c>
     </row>
     <row r="377" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13032,16 +13019,16 @@
         <v>376</v>
       </c>
       <c r="B377" s="1" t="s">
+        <v>1670</v>
+      </c>
+      <c r="C377" s="1" t="s">
         <v>1671</v>
       </c>
-      <c r="C377" s="1" t="s">
+      <c r="D377" s="1" t="s">
         <v>1672</v>
       </c>
-      <c r="D377" s="1" t="s">
+      <c r="E377" s="1" t="s">
         <v>1673</v>
-      </c>
-      <c r="E377" s="1" t="s">
-        <v>1674</v>
       </c>
     </row>
     <row r="378" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13049,16 +13036,16 @@
         <v>377</v>
       </c>
       <c r="B378" s="1" t="s">
+        <v>1674</v>
+      </c>
+      <c r="C378" s="1" t="s">
         <v>1675</v>
       </c>
-      <c r="C378" s="1" t="s">
+      <c r="D378" s="1" t="s">
         <v>1676</v>
       </c>
-      <c r="D378" s="1" t="s">
+      <c r="E378" s="1" t="s">
         <v>1677</v>
-      </c>
-      <c r="E378" s="1" t="s">
-        <v>1678</v>
       </c>
     </row>
     <row r="379" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13066,16 +13053,16 @@
         <v>378</v>
       </c>
       <c r="B379" s="1" t="s">
+        <v>1678</v>
+      </c>
+      <c r="C379" s="1" t="s">
         <v>1679</v>
       </c>
-      <c r="C379" s="1" t="s">
+      <c r="D379" s="1" t="s">
         <v>1680</v>
       </c>
-      <c r="D379" s="1" t="s">
-        <v>1681</v>
-      </c>
       <c r="E379" s="1" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="380" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13083,16 +13070,16 @@
         <v>379</v>
       </c>
       <c r="B380" s="1" t="s">
+        <v>1681</v>
+      </c>
+      <c r="C380" s="1" t="s">
         <v>1682</v>
       </c>
-      <c r="C380" s="1" t="s">
+      <c r="D380" s="1" t="s">
         <v>1683</v>
       </c>
-      <c r="D380" s="1" t="s">
+      <c r="E380" s="1" t="s">
         <v>1684</v>
-      </c>
-      <c r="E380" s="1" t="s">
-        <v>1685</v>
       </c>
     </row>
     <row r="381" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13100,16 +13087,16 @@
         <v>380</v>
       </c>
       <c r="B381" s="1" t="s">
+        <v>1685</v>
+      </c>
+      <c r="C381" s="1" t="s">
         <v>1686</v>
       </c>
-      <c r="C381" s="1" t="s">
+      <c r="D381" s="1" t="s">
         <v>1687</v>
       </c>
-      <c r="D381" s="1" t="s">
+      <c r="E381" s="1" t="s">
         <v>1688</v>
-      </c>
-      <c r="E381" s="1" t="s">
-        <v>1689</v>
       </c>
     </row>
     <row r="382" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13117,16 +13104,16 @@
         <v>381</v>
       </c>
       <c r="B382" s="1" t="s">
+        <v>1689</v>
+      </c>
+      <c r="C382" s="1" t="s">
         <v>1690</v>
       </c>
-      <c r="C382" s="1" t="s">
+      <c r="D382" s="1" t="s">
         <v>1691</v>
       </c>
-      <c r="D382" s="1" t="s">
+      <c r="E382" s="1" t="s">
         <v>1692</v>
-      </c>
-      <c r="E382" s="1" t="s">
-        <v>1693</v>
       </c>
     </row>
     <row r="383" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13134,16 +13121,16 @@
         <v>382</v>
       </c>
       <c r="B383" s="1" t="s">
+        <v>1693</v>
+      </c>
+      <c r="C383" s="1" t="s">
         <v>1694</v>
       </c>
-      <c r="C383" s="1" t="s">
+      <c r="D383" s="1" t="s">
         <v>1695</v>
       </c>
-      <c r="D383" s="1" t="s">
+      <c r="E383" s="1" t="s">
         <v>1696</v>
-      </c>
-      <c r="E383" s="1" t="s">
-        <v>1697</v>
       </c>
     </row>
     <row r="384" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13151,16 +13138,16 @@
         <v>383</v>
       </c>
       <c r="B384" s="1" t="s">
+        <v>1697</v>
+      </c>
+      <c r="C384" s="1" t="s">
         <v>1698</v>
       </c>
-      <c r="C384" s="1" t="s">
+      <c r="D384" s="1" t="s">
         <v>1699</v>
       </c>
-      <c r="D384" s="1" t="s">
+      <c r="E384" s="1" t="s">
         <v>1700</v>
-      </c>
-      <c r="E384" s="1" t="s">
-        <v>1701</v>
       </c>
     </row>
     <row r="385" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13168,16 +13155,16 @@
         <v>384</v>
       </c>
       <c r="B385" s="1" t="s">
+        <v>1701</v>
+      </c>
+      <c r="C385" s="1" t="s">
         <v>1702</v>
       </c>
-      <c r="C385" s="1" t="s">
+      <c r="D385" s="1" t="s">
         <v>1703</v>
       </c>
-      <c r="D385" s="1" t="s">
+      <c r="E385" s="1" t="s">
         <v>1704</v>
-      </c>
-      <c r="E385" s="1" t="s">
-        <v>1705</v>
       </c>
     </row>
     <row r="386" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13185,16 +13172,16 @@
         <v>385</v>
       </c>
       <c r="B386" s="1" t="s">
+        <v>1705</v>
+      </c>
+      <c r="C386" s="1" t="s">
         <v>1706</v>
       </c>
-      <c r="C386" s="1" t="s">
+      <c r="D386" s="1" t="s">
         <v>1707</v>
       </c>
-      <c r="D386" s="1" t="s">
-        <v>1708</v>
-      </c>
       <c r="E386" s="1" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="387" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13202,16 +13189,16 @@
         <v>386</v>
       </c>
       <c r="B387" s="1" t="s">
+        <v>1708</v>
+      </c>
+      <c r="C387" s="1" t="s">
         <v>1709</v>
       </c>
-      <c r="C387" s="1" t="s">
+      <c r="D387" s="1" t="s">
         <v>1710</v>
       </c>
-      <c r="D387" s="1" t="s">
+      <c r="E387" s="1" t="s">
         <v>1711</v>
-      </c>
-      <c r="E387" s="1" t="s">
-        <v>1712</v>
       </c>
     </row>
     <row r="388" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13219,16 +13206,16 @@
         <v>387</v>
       </c>
       <c r="B388" s="1" t="s">
+        <v>1712</v>
+      </c>
+      <c r="C388" s="1" t="s">
         <v>1713</v>
       </c>
-      <c r="C388" s="1" t="s">
+      <c r="D388" s="1" t="s">
         <v>1714</v>
       </c>
-      <c r="D388" s="1" t="s">
+      <c r="E388" s="1" t="s">
         <v>1715</v>
-      </c>
-      <c r="E388" s="1" t="s">
-        <v>1716</v>
       </c>
     </row>
     <row r="389" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13236,16 +13223,16 @@
         <v>388</v>
       </c>
       <c r="B389" s="1" t="s">
+        <v>1716</v>
+      </c>
+      <c r="C389" s="1" t="s">
         <v>1717</v>
       </c>
-      <c r="C389" s="1" t="s">
+      <c r="D389" s="1" t="s">
         <v>1718</v>
       </c>
-      <c r="D389" s="1" t="s">
+      <c r="E389" s="1" t="s">
         <v>1719</v>
-      </c>
-      <c r="E389" s="1" t="s">
-        <v>1720</v>
       </c>
     </row>
     <row r="390" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13253,16 +13240,16 @@
         <v>389</v>
       </c>
       <c r="B390" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="C390" s="1" t="s">
         <v>1721</v>
       </c>
-      <c r="C390" s="1" t="s">
+      <c r="D390" s="1" t="s">
         <v>1722</v>
       </c>
-      <c r="D390" s="1" t="s">
+      <c r="E390" s="1" t="s">
         <v>1723</v>
-      </c>
-      <c r="E390" s="1" t="s">
-        <v>1724</v>
       </c>
     </row>
     <row r="391" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13270,16 +13257,16 @@
         <v>390</v>
       </c>
       <c r="B391" s="1" t="s">
+        <v>1724</v>
+      </c>
+      <c r="C391" s="1" t="s">
         <v>1725</v>
       </c>
-      <c r="C391" s="1" t="s">
+      <c r="D391" s="1" t="s">
         <v>1726</v>
       </c>
-      <c r="D391" s="1" t="s">
+      <c r="E391" s="1" t="s">
         <v>1727</v>
-      </c>
-      <c r="E391" s="1" t="s">
-        <v>1728</v>
       </c>
     </row>
     <row r="392" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13287,16 +13274,16 @@
         <v>391</v>
       </c>
       <c r="B392" s="1" t="s">
+        <v>1728</v>
+      </c>
+      <c r="C392" s="1" t="s">
         <v>1729</v>
       </c>
-      <c r="C392" s="1" t="s">
+      <c r="D392" s="1" t="s">
         <v>1730</v>
       </c>
-      <c r="D392" s="1" t="s">
+      <c r="E392" s="1" t="s">
         <v>1731</v>
-      </c>
-      <c r="E392" s="1" t="s">
-        <v>1732</v>
       </c>
     </row>
     <row r="393" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13304,16 +13291,16 @@
         <v>392</v>
       </c>
       <c r="B393" s="1" t="s">
+        <v>1732</v>
+      </c>
+      <c r="C393" s="1" t="s">
         <v>1733</v>
       </c>
-      <c r="C393" s="1" t="s">
+      <c r="D393" s="1" t="s">
         <v>1734</v>
       </c>
-      <c r="D393" s="1" t="s">
+      <c r="E393" s="1" t="s">
         <v>1735</v>
-      </c>
-      <c r="E393" s="1" t="s">
-        <v>1736</v>
       </c>
     </row>
     <row r="394" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13321,16 +13308,16 @@
         <v>393</v>
       </c>
       <c r="B394" s="1" t="s">
+        <v>1736</v>
+      </c>
+      <c r="C394" s="1" t="s">
         <v>1737</v>
       </c>
-      <c r="C394" s="1" t="s">
+      <c r="D394" s="1" t="s">
         <v>1738</v>
       </c>
-      <c r="D394" s="1" t="s">
-        <v>1739</v>
-      </c>
       <c r="E394" s="1" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="395" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13338,16 +13325,16 @@
         <v>394</v>
       </c>
       <c r="B395" s="1" t="s">
+        <v>1739</v>
+      </c>
+      <c r="C395" s="1" t="s">
         <v>1740</v>
       </c>
-      <c r="C395" s="1" t="s">
+      <c r="D395" s="1" t="s">
         <v>1741</v>
       </c>
-      <c r="D395" s="1" t="s">
+      <c r="E395" s="1" t="s">
         <v>1742</v>
-      </c>
-      <c r="E395" s="1" t="s">
-        <v>1743</v>
       </c>
     </row>
     <row r="396" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13355,16 +13342,16 @@
         <v>395</v>
       </c>
       <c r="B396" s="1" t="s">
+        <v>1743</v>
+      </c>
+      <c r="C396" s="1" t="s">
         <v>1744</v>
       </c>
-      <c r="C396" s="1" t="s">
+      <c r="D396" s="1" t="s">
         <v>1745</v>
       </c>
-      <c r="D396" s="1" t="s">
+      <c r="E396" s="1" t="s">
         <v>1746</v>
-      </c>
-      <c r="E396" s="1" t="s">
-        <v>1747</v>
       </c>
     </row>
     <row r="397" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13372,16 +13359,16 @@
         <v>396</v>
       </c>
       <c r="B397" s="1" t="s">
+        <v>1747</v>
+      </c>
+      <c r="C397" s="1" t="s">
         <v>1748</v>
       </c>
-      <c r="C397" s="1" t="s">
+      <c r="D397" s="1" t="s">
         <v>1749</v>
       </c>
-      <c r="D397" s="1" t="s">
+      <c r="E397" s="1" t="s">
         <v>1750</v>
-      </c>
-      <c r="E397" s="1" t="s">
-        <v>1751</v>
       </c>
     </row>
     <row r="398" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13389,16 +13376,16 @@
         <v>397</v>
       </c>
       <c r="B398" s="1" t="s">
+        <v>1751</v>
+      </c>
+      <c r="C398" s="1" t="s">
         <v>1752</v>
       </c>
-      <c r="C398" s="1" t="s">
+      <c r="D398" s="1" t="s">
         <v>1753</v>
       </c>
-      <c r="D398" s="1" t="s">
+      <c r="E398" s="1" t="s">
         <v>1754</v>
-      </c>
-      <c r="E398" s="1" t="s">
-        <v>1755</v>
       </c>
     </row>
     <row r="399" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13406,16 +13393,16 @@
         <v>398</v>
       </c>
       <c r="B399" s="1" t="s">
+        <v>1755</v>
+      </c>
+      <c r="C399" s="1" t="s">
         <v>1756</v>
       </c>
-      <c r="C399" s="1" t="s">
+      <c r="D399" s="1" t="s">
         <v>1757</v>
       </c>
-      <c r="D399" s="1" t="s">
+      <c r="E399" s="1" t="s">
         <v>1758</v>
-      </c>
-      <c r="E399" s="1" t="s">
-        <v>1759</v>
       </c>
     </row>
     <row r="400" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13423,16 +13410,16 @@
         <v>399</v>
       </c>
       <c r="B400" s="1" t="s">
+        <v>1759</v>
+      </c>
+      <c r="C400" s="1" t="s">
         <v>1760</v>
       </c>
-      <c r="C400" s="1" t="s">
+      <c r="D400" s="1" t="s">
         <v>1761</v>
       </c>
-      <c r="D400" s="1" t="s">
-        <v>1762</v>
-      </c>
       <c r="E400" s="1" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="401" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13440,16 +13427,16 @@
         <v>400</v>
       </c>
       <c r="B401" s="1" t="s">
+        <v>1762</v>
+      </c>
+      <c r="C401" s="1" t="s">
         <v>1763</v>
       </c>
-      <c r="C401" s="1" t="s">
+      <c r="D401" s="1" t="s">
         <v>1764</v>
       </c>
-      <c r="D401" s="1" t="s">
+      <c r="E401" s="1" t="s">
         <v>1765</v>
-      </c>
-      <c r="E401" s="1" t="s">
-        <v>1766</v>
       </c>
     </row>
     <row r="402" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
